--- a/corpus/xlsx/level-091/template.xlsx
+++ b/corpus/xlsx/level-091/template.xlsx
@@ -39,25 +39,25 @@
   <!-- fixture padding 10 -->
   <pkg:definedNames>
     <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange1">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange2">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange3">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange4">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange5">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange6">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange7">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange8">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange9">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange10">'Report'!$A$40:$D$40</pkg:definedName>
+    <pkg:definedName name="ItemRange1">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange2">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange3">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange4">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange5">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange6">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange7">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange8">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange9">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange10">'Report'!$A$40:$D$41</pkg:definedName>
     <!-- fixture padding 10 -->
   </pkg:definedNames>
   <!-- fixture padding 10 -->
@@ -68,7 +68,7 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 10 -->
-<pkg:sst xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
+<pkg:sst xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="66">
   <!-- fixture padding 10 -->
   <pkg:si>
     <!-- fixture padding 10 -->
@@ -264,6 +264,138 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">l</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
@@ -280,6 +412,70 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">us</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">t</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
@@ -296,6 +492,614 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">o</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">m</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">r}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">o</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">u</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">n</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">s</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">p</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">n</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">b</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">l</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">l</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">i</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
@@ -328,10 +1132,478 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">r</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">l}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">N</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">m</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">Q</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">u</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">n</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">y</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">P</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">r</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">T</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">o</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">l</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
     <pkg:r>
       <!-- fixture padding 10 -->
       <pkg:rPr>
@@ -360,23 +1632,87 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
+      <pkg:t xml:space="preserve">ms</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">[i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">]</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.n</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">am</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -396,6 +1732,170 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">{d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">te</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ms</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">[i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">].</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">qu</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">an</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ti</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ty}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
@@ -412,6 +1912,154 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">em</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">s[</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">].</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">pr</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ic</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
@@ -428,1259 +2076,103 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">st</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">o</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">m</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">o</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">n</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">s</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">p</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">d</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">n</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">b</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">d</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">N</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">m</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">Q</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">n</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">y</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">P</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">T</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">o</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">#e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">ac</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">h i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">te</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">ms</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{n</pkg:t>
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">em</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">s[</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i+</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">1]</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.n</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1712,319 +2204,7 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e}}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">q</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">an</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">y</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-  </pkg:si>
-  <!-- fixture padding 10 -->
-  <pkg:si>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">p</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
+      <pkg:t xml:space="preserve">e}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -9722,7 +9902,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -9784,7 +9964,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -9846,7 +10026,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -9908,7 +10088,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -9970,7 +10150,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -10032,7 +10212,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -10094,7 +10274,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -10156,7 +10336,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -10218,7 +10398,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -10280,7 +10460,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -10327,9 +10507,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 10 -->
-<pkg:table xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D40" totalsRowShown="0">
-  <!-- fixture padding 10 -->
-  <pkg:autoFilter ref="A39:D40"/>
+<pkg:table xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D41" totalsRowShown="0">
+  <!-- fixture padding 10 -->
+  <pkg:autoFilter ref="A39:D41"/>
   <!-- fixture padding 10 -->
   <pkg:tableColumns count="4">
     <!-- fixture padding 10 -->
@@ -10352,7 +10532,7 @@
 <!-- fixture padding 10 -->
 <pkg:worksheet xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <!-- fixture padding 10 -->
-  <pkg:dimension ref="A1:J139"/>
+  <pkg:dimension ref="A1:J140"/>
   <!-- fixture padding 10 -->
   <!-- fixture padding 10 -->
   <pkg:sheetFormatPr defaultRowHeight="15"/>
@@ -11007,33 +11187,33 @@
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="E40" s="0" t="inlineStr">
-        <!-- fixture padding 10 -->
-        <pkg:is>
-          <!-- fixture padding 10 -->
-          <pkg:t xml:space="preserve">{{/each}}</pkg:t>
-          <!-- fixture padding 10 -->
-        </pkg:is>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="100">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A100" s="0" t="s">
+    <pkg:row r="41">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A41" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>14</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="B100" s="0" t="s">
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="101">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A101" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>15</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B101" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C100" s="0">
+      <pkg:c r="C101" s="0">
         <!-- fixture padding 10 -->
         <pkg:v>0</pkg:v>
         <!-- fixture padding 10 -->
@@ -11041,867 +11221,867 @@
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="101">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A101" s="0" t="s">
+    <pkg:row r="102">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A102" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>16</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B102" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C102" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>1</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="103">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A103" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>17</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B103" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C103" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="104">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A104" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>18</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B104" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C104" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>3</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="105">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A105" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>19</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B105" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C105" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>4</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="106">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A106" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>20</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B106" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C106" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>5</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="107">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A107" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>21</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B107" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C107" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>6</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="108">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A108" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>22</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B108" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C108" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>7</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="109">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A109" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>23</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B109" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C109" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>8</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="110">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A110" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>24</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B110" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C110" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>9</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="111">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A111" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>25</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B111" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C111" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>10</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="112">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A112" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>26</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B112" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C112" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>11</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="113">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A113" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>27</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B113" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C113" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>12</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="114">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A114" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>28</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B114" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C114" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>13</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="115">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A115" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>29</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B115" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C115" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>14</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="116">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A116" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>30</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B116" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C116" s="0">
         <!-- fixture padding 10 -->
         <pkg:v>15</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="B101" s="0" t="s">
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="117">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A117" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>31</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B117" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C101" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>1</pkg:v>
+      <pkg:c r="C117" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>16</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="102">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A102" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>16</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B102" s="0" t="s">
+    <pkg:row r="118">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A118" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>32</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B118" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C102" s="0">
+      <pkg:c r="C118" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>17</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="119">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A119" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>33</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B119" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
+      <pkg:c r="C119" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>18</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="103">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A103" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>17</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B103" s="0" t="s">
+    <pkg:row r="120">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A120" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>34</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B120" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C103" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>3</pkg:v>
+      <pkg:c r="C120" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>19</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="104">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A104" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>18</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B104" s="0" t="s">
+    <pkg:row r="121">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A121" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>35</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B121" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C104" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>4</pkg:v>
+      <pkg:c r="C121" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>20</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="105">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A105" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>19</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B105" s="0" t="s">
+    <pkg:row r="122">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A122" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>36</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B122" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C105" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>5</pkg:v>
+      <pkg:c r="C122" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>21</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="106">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A106" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>20</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B106" s="0" t="s">
+    <pkg:row r="123">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A123" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>37</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B123" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C106" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>6</pkg:v>
+      <pkg:c r="C123" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>22</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="107">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A107" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>21</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B107" s="0" t="s">
+    <pkg:row r="124">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A124" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>38</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B124" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C107" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>7</pkg:v>
+      <pkg:c r="C124" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>23</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="108">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A108" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>22</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B108" s="0" t="s">
+    <pkg:row r="125">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A125" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>39</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B125" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C108" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>8</pkg:v>
+      <pkg:c r="C125" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>24</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="109">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A109" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>23</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B109" s="0" t="s">
+    <pkg:row r="126">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A126" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>40</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B126" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C109" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>9</pkg:v>
+      <pkg:c r="C126" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>25</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="110">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A110" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>24</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B110" s="0" t="s">
+    <pkg:row r="127">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A127" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>41</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B127" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C110" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>10</pkg:v>
+      <pkg:c r="C127" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>26</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="111">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A111" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>25</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B111" s="0" t="s">
+    <pkg:row r="128">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A128" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>42</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B128" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C111" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>11</pkg:v>
+      <pkg:c r="C128" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>27</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="112">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A112" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>26</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B112" s="0" t="s">
+    <pkg:row r="129">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A129" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>43</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B129" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C112" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>12</pkg:v>
+      <pkg:c r="C129" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>28</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="113">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A113" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>27</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B113" s="0" t="s">
+    <pkg:row r="130">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A130" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>44</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B130" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C113" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>13</pkg:v>
+      <pkg:c r="C130" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>29</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="114">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A114" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>28</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B114" s="0" t="s">
+    <pkg:row r="131">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A131" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>45</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B131" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C114" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>14</pkg:v>
+      <pkg:c r="C131" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>30</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="115">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A115" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>29</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B115" s="0" t="s">
+    <pkg:row r="132">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A132" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>46</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B132" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C115" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>15</pkg:v>
+      <pkg:c r="C132" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>31</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="116">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A116" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>30</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B116" s="0" t="s">
+    <pkg:row r="133">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A133" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>47</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B133" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C116" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>16</pkg:v>
+      <pkg:c r="C133" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>32</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="117">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A117" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>31</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B117" s="0" t="s">
+    <pkg:row r="134">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A134" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>48</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B134" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C117" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>17</pkg:v>
+      <pkg:c r="C134" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>33</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="118">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A118" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>32</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B118" s="0" t="s">
+    <pkg:row r="135">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A135" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>49</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B135" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C118" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>18</pkg:v>
+      <pkg:c r="C135" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>34</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="119">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A119" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>33</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B119" s="0" t="s">
+    <pkg:row r="136">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A136" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>50</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B136" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C119" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>19</pkg:v>
+      <pkg:c r="C136" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>35</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="120">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A120" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>34</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B120" s="0" t="s">
+    <pkg:row r="137">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A137" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>51</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B137" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C120" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>20</pkg:v>
+      <pkg:c r="C137" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>36</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="121">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A121" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>35</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B121" s="0" t="s">
+    <pkg:row r="138">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A138" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>52</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B138" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C121" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>21</pkg:v>
+      <pkg:c r="C138" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>37</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="122">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A122" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>36</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B122" s="0" t="s">
+    <pkg:row r="139">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A139" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>53</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B139" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C122" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>22</pkg:v>
+      <pkg:c r="C139" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>38</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="123">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A123" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>37</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B123" s="0" t="s">
+    <pkg:row r="140">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A140" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>54</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B140" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C123" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>23</pkg:v>
+      <pkg:c r="C140" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>39</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="124">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A124" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>38</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B124" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C124" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>24</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="125">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A125" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>39</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B125" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C125" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>25</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="126">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A126" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>40</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B126" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C126" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>26</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="127">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A127" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>41</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B127" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C127" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>27</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="128">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A128" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>42</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B128" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C128" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>28</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="129">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A129" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>43</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B129" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C129" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>29</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="130">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A130" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>44</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B130" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C130" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>30</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="131">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A131" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>45</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B131" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C131" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>31</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="132">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A132" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>46</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B132" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C132" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>32</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="133">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A133" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>47</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B133" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C133" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>33</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="134">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A134" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>48</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B134" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C134" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>34</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="135">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A135" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>49</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B135" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C135" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>35</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="136">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A136" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>50</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B136" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C136" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>36</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="137">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A137" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>51</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B137" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C137" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>37</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="138">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A138" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>52</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B138" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C138" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>38</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="139">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A139" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>53</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B139" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C139" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>39</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
   </pkg:sheetData>
   <!-- fixture padding 10 -->
-  <pkg:autoFilter ref="A39:D40"/>
+  <pkg:autoFilter ref="A39:D41"/>
   <!-- fixture padding 10 -->
   <pkg:mergeCells count="10">
     <!-- fixture padding 10 -->
@@ -11927,7 +12107,7 @@
     <!-- fixture padding 10 -->
   </pkg:mergeCells>
   <!-- fixture padding 10 -->
-  <pkg:conditionalFormatting sqref="B40:B40">
+  <pkg:conditionalFormatting sqref="B40:B41">
     <!-- fixture padding 10 -->
     <pkg:cfRule type="cellIs" priority="1" operator="greaterThan">
       <!-- fixture padding 10 -->
@@ -11939,7 +12119,7 @@
   <!-- fixture padding 10 -->
   <pkg:dataValidations count="8">
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11947,7 +12127,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11955,7 +12135,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11963,7 +12143,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11971,7 +12151,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11979,7 +12159,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11987,7 +12167,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -11995,7 +12175,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -12030,7 +12210,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>62</pkg:v>
+        <pkg:v>63</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12075,7 +12255,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>63</pkg:v>
+        <pkg:v>64</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12120,7 +12300,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>64</pkg:v>
+        <pkg:v>65</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12165,7 +12345,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>54</pkg:v>
+        <pkg:v>55</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12210,7 +12390,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>55</pkg:v>
+        <pkg:v>56</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12255,7 +12435,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>56</pkg:v>
+        <pkg:v>57</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12300,7 +12480,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>57</pkg:v>
+        <pkg:v>58</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12345,7 +12525,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>58</pkg:v>
+        <pkg:v>59</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12390,7 +12570,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>59</pkg:v>
+        <pkg:v>60</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12435,7 +12615,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>60</pkg:v>
+        <pkg:v>61</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -12480,7 +12660,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>61</pkg:v>
+        <pkg:v>62</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
